--- a/crossref_retrieved_authors.xlsx
+++ b/crossref_retrieved_authors.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1326"/>
+  <dimension ref="A1:B1335"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -16266,6 +16266,114 @@
         </is>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>10.4324/9781032633275-7</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>[{"given":"Amos","family":"Tversky","sequence":"first"},{"given":"Itamar","family":"Gati","sequence":"additional"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>10.1002/bdm.2041</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>[{"ORCID":"https://orcid.org/0000-0002-3283-5278","authenticated.orcid":false,"given":"Arnoud","family":"Plantinga","sequence":"first","affiliation.name":"Department of Social Psychology/TIBER Tilburg University  Tilburg The Netherlands"},{"given":"Job M.T.","family":"Krijnen","sequence":"additional","affiliation.name":"Anderson School of Management University of California  Los Angeles CA USA"},{"given":"Marcel","family":"Zeelenberg","sequence":"additional","affiliation1.name":"Department of Social Psychology/TIBER Tilburg University  Tilburg The Netherlands","affiliation2.name":"Department of Marketing Vrije Universiteit Amsterdam  Amsterdam The Netherlands"},{"given":"Seger M.","family":"Breugelmans","sequence":"additional","affiliation.name":"Department of Social Psychology/TIBER Tilburg University  Tilburg The Netherlands"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>10.1080/17439760.2017.1279210</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>[{"given":"Kristin","family":"Layous","sequence":"first","affiliation1.name":"Department of Psychology, California State University, East Bay, Hayward, CA, USA","affiliation2.name":"Department of Psychology, University of California, Riverside, CA, USA"},{"given":"Jaime","family":"Kurtz","sequence":"additional","affiliation.name":"Department of Psychology, James Madison University, Harrisonburg, VA, USA"},{"given":"Joseph","family":"Chancellor","sequence":"additional","affiliation.name":"Department of Psychology, Cambridge University, Cambridge, United Kingdom"},{"given":"Sonja","family":"Lyubomirsky","sequence":"additional","affiliation.name":"Department of Psychology, University of California, Riverside, CA, USA"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>10.1016/j.joep.2018.12.001</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>[{"given":"Anuj K.","family":"Shah","sequence":"first"},{"given":"Sendhil","family":"Mullainathan","sequence":"additional"},{"given":"Eldar","family":"Shafir","sequence":"additional"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>10.1521/soco.2018.36.1.4</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>[{"given":"Anuj K.","family":"Shah","sequence":"first","affiliation.name":"University of Chicago."},{"given":"Jiaying","family":"Zhao","sequence":"additional","affiliation.name":"University of British Columbia."},{"given":"Sendhil","family":"Mullainathan","sequence":"additional","affiliation.name":"Harvard University."},{"given":"Eldar","family":"Shafir","sequence":"additional","affiliation.name":"Princeton University."}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>10.1080/00224545.2016.1270892</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>[{"given":"Andrew A.","family":"Abeyta","sequence":"first","affiliation.name":"North Dakota State University"},{"given":"Clay","family":"Routledge","sequence":"additional","affiliation.name":"North Dakota State University"},{"given":"Michael","family":"Kersten","sequence":"additional","affiliation.name":"Texas Christian University"},{"given":"Cathy R.","family":"Cox","sequence":"additional","affiliation.name":"Texas Christian University"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>10.1177/0146167202286008</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>[{"given":"Emily","family":"Pronin","sequence":"first","affiliation.name":"Stanford University,"},{"given":"Daniel Y.","family":"Lin","sequence":"additional","affiliation.name":"Stanford University"},{"given":"Lee","family":"Ross","sequence":"additional","affiliation.name":"Stanford University"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>10.1371/journal.pone.0163051</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>[{"given":"Warren K.","family":"Bickel","sequence":"first"},{"given":"A. George","family":"Wilson","sequence":"additional"},{"given":"Chen","family":"Chen","sequence":"additional"},{"given":"Mikhail N.","family":"Koffarnus","sequence":"additional"},{"given":"Christopher T.","family":"Franck","sequence":"additional"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>10.1177/1948550614555029</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>[{"given":"Lydia F.","family":"Emery","sequence":"first","affiliation.name":"Northwestern University, Evanston, IL, USA"},{"given":"Courtney","family":"Walsh","sequence":"additional","affiliation.name":"University of Texas at Austin, Austin, TX, USA"},{"given":"Erica B.","family":"Slotter","sequence":"additional","affiliation.name":"Villanova University, Villanova, PA, USA"}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
